--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 20:08</t>
+    <t xml:space="preserve">2026-08-05 11:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:06</t>
+    <t xml:space="preserve">2026-08-16 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:13</t>
+    <t xml:space="preserve">2026-08-19 14:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:39</t>
+    <t xml:space="preserve">2026-08-28 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_aysen.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:36</t>
+    <t xml:space="preserve">2026-09-06 17:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
